--- a/GBDS MARCH FILES 2026/PRICE LIST January.xlsx
+++ b/GBDS MARCH FILES 2026/PRICE LIST January.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34B0C8E-DF8C-4EC5-9F74-6DD939A8A381}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98265E36-EA1E-487E-9FC1-6D85819CBB26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J30" s="8"/>
       <c r="K30" s="9">
-        <f t="shared" ref="K30:K61" si="9">C30/2</f>
+        <f t="shared" ref="K30:K59" si="9">C30/2</f>
         <v>791</v>
       </c>
     </row>

--- a/GBDS MARCH FILES 2026/PRICE LIST January.xlsx
+++ b/GBDS MARCH FILES 2026/PRICE LIST January.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98265E36-EA1E-487E-9FC1-6D85819CBB26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA20B92-B7D8-4549-A666-2F2208A8E25D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
